--- a/data/trans_orig/ED_ADU-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media del adulto entrevistado</t>
+          <t>Edad media del adulto entrevistado (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,04</t>
+          <t>19,54; 20,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,81; 20,31</t>
+          <t>19,8; 20,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,01; 20,48</t>
+          <t>19,99; 20,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,75; 20,51</t>
+          <t>19,76; 20,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 20,53</t>
+          <t>20,03; 20,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,11; 20,63</t>
+          <t>20,14; 20,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,61; 21,1</t>
+          <t>20,59; 21,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 20,61</t>
+          <t>19,94; 20,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,87; 20,21</t>
+          <t>19,88; 20,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,02; 20,37</t>
+          <t>20,03; 20,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,36; 20,7</t>
+          <t>20,35; 20,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 20,5</t>
+          <t>19,97; 20,48</t>
         </is>
       </c>
     </row>
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,87; 29,29</t>
+          <t>28,86; 29,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 29,69</t>
+          <t>29,24; 29,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 29,52</t>
+          <t>29,02; 29,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,4; 30,1</t>
+          <t>29,42; 30,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,31; 29,79</t>
+          <t>29,32; 29,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,51; 29,96</t>
+          <t>29,53; 29,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 30,01</t>
+          <t>29,53; 29,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,48; 31,76</t>
+          <t>29,5; 31,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,43; 29,75</t>
+          <t>29,44; 29,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 29,67</t>
+          <t>29,33; 29,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 31,02</t>
+          <t>29,57; 31,04</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,61; 40,09</t>
+          <t>39,59; 40,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,44; 39,88</t>
+          <t>39,45; 39,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,15; 39,64</t>
+          <t>39,15; 39,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,66; 40,17</t>
+          <t>39,66; 40,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 39,92</t>
+          <t>39,47; 39,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,35; 39,81</t>
+          <t>39,35; 39,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,28; 39,75</t>
+          <t>39,3; 39,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,6; 40,44</t>
+          <t>39,59; 40,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,6; 39,91</t>
+          <t>39,59; 39,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,47; 39,79</t>
+          <t>39,46; 39,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,28; 39,61</t>
+          <t>39,31; 39,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,7; 40,17</t>
+          <t>39,7; 40,2</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1136,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,02; 49,59</t>
+          <t>49,06; 49,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,56; 49,03</t>
+          <t>48,54; 49,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,12; 49,64</t>
+          <t>49,16; 49,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,32; 50,47</t>
+          <t>49,31; 50,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,87; 49,42</t>
+          <t>48,89; 49,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,98; 49,49</t>
+          <t>48,97; 49,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,09; 49,59</t>
+          <t>49,08; 49,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,05; 49,43</t>
+          <t>49,04; 49,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,84; 49,2</t>
+          <t>48,82; 49,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,2; 49,55</t>
+          <t>49,18; 49,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,21; 50,11</t>
+          <t>49,22; 50,07</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,54; 60,19</t>
+          <t>59,55; 60,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,95; 59,56</t>
+          <t>58,95; 59,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1296,22 +1296,22 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,23; 59,84</t>
+          <t>59,22; 59,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,05; 59,68</t>
+          <t>59,07; 59,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,3; 59,87</t>
+          <t>59,29; 59,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,97; 59,34</t>
+          <t>58,97; 59,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,08; 59,54</t>
+          <t>59,09; 59,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,23; 59,63</t>
+          <t>59,2; 59,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,03; 59,32</t>
+          <t>59,05; 59,35</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,83; 69,56</t>
+          <t>68,86; 69,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,34; 70,05</t>
+          <t>69,35; 70,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,0; 69,62</t>
+          <t>69,05; 69,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,1; 69,57</t>
+          <t>69,08; 69,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,74; 69,36</t>
+          <t>68,78; 69,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,69; 69,32</t>
+          <t>68,66; 69,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,99; 69,62</t>
+          <t>69,0; 69,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67,63; 69,26</t>
+          <t>67,63; 69,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,89; 69,36</t>
+          <t>68,88; 69,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 69,56</t>
+          <t>69,08; 69,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 69,51</t>
+          <t>69,08; 69,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67,98; 69,29</t>
+          <t>67,93; 69,31</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,84; 80,01</t>
+          <t>78,78; 79,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,26; 80,35</t>
+          <t>79,26; 80,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,74; 80,64</t>
+          <t>79,78; 80,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81,1; 82,06</t>
+          <t>81,09; 82,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,28; 79,12</t>
+          <t>78,32; 79,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,42; 80,4</t>
+          <t>79,42; 80,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,79; 80,87</t>
+          <t>79,76; 80,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81,66; 82,48</t>
+          <t>81,69; 82,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,63; 79,34</t>
+          <t>78,64; 79,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79,49; 80,22</t>
+          <t>79,46; 80,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,87; 80,62</t>
+          <t>79,88; 80,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,53; 82,17</t>
+          <t>81,56; 82,19</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,78; 44,02</t>
+          <t>42,79; 44,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,12; 45,39</t>
+          <t>44,16; 45,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,43; 46,6</t>
+          <t>45,43; 46,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,74; 49,38</t>
+          <t>47,7; 49,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,13; 46,39</t>
+          <t>45,11; 46,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,41; 47,64</t>
+          <t>46,43; 47,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,57; 48,89</t>
+          <t>47,66; 48,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,73; 53,93</t>
+          <t>49,79; 53,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44,15; 45,09</t>
+          <t>44,17; 45,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45,5; 46,38</t>
+          <t>45,48; 46,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,71; 47,6</t>
+          <t>46,73; 47,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,09; 51,75</t>
+          <t>49,09; 51,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_ADU-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ED_ADU-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,15</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,28</t>
+          <t>20,29</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,21</t>
+          <t>20,35</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,02</t>
+          <t>19,55; 20,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 20,28</t>
+          <t>19,78; 20,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,99; 20,48</t>
+          <t>19,96; 20,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 20,49</t>
+          <t>20,03; 20,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 20,52</t>
+          <t>20,06; 20,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,14; 20,63</t>
+          <t>20,12; 20,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,59; 21,13</t>
+          <t>20,61; 21,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 20,65</t>
+          <t>19,95; 20,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,88; 20,21</t>
+          <t>19,86; 20,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 20,39</t>
+          <t>20,02; 20,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 20,72</t>
+          <t>20,36; 20,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 20,48</t>
+          <t>20,1; 20,6</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,73</t>
+          <t>29,76</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,18</t>
+          <t>29,62</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,98</t>
+          <t>29,69</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,86; 29,3</t>
+          <t>28,88; 29,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 29,68</t>
+          <t>29,23; 29,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 29,51</t>
+          <t>29,01; 29,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 30,09</t>
+          <t>29,45; 30,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 29,8</t>
+          <t>29,29; 29,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 29,99</t>
+          <t>29,51; 29,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 29,99</t>
+          <t>29,51; 29,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,5; 31,64</t>
+          <t>29,34; 29,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,15; 29,46</t>
+          <t>29,13; 29,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,44; 29,77</t>
+          <t>29,43; 29,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,33; 29,68</t>
+          <t>29,34; 29,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 31,04</t>
+          <t>29,46; 29,88</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,92</t>
+          <t>39,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,87</t>
+          <t>39,68</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,89</t>
+          <t>39,79</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,59; 40,08</t>
+          <t>39,6; 40,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>39,45; 39,89</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39,16; 39,64</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39,65; 40,13</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>39,45; 39,92</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39,15; 39,62</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39,66; 40,18</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>39,47; 39,91</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,35; 39,8</t>
+          <t>39,36; 39,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,3; 39,74</t>
+          <t>39,29; 39,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,59; 40,36</t>
+          <t>39,51; 39,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,59; 39,92</t>
+          <t>39,61; 39,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,46; 39,77</t>
+          <t>39,48; 39,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,31; 39,63</t>
+          <t>39,3; 39,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,7; 40,2</t>
+          <t>39,63; 39,95</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,84</t>
+          <t>49,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,17</t>
+          <t>49,24</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,54</t>
+          <t>49,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,06; 49,62</t>
+          <t>49,04; 49,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,54; 49,02</t>
+          <t>48,54; 49,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,16; 49,65</t>
+          <t>49,15; 49,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,31; 50,52</t>
+          <t>49,09; 49,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,89; 49,4</t>
+          <t>48,87; 49,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,97; 49,48</t>
+          <t>48,97; 49,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,08; 49,58</t>
+          <t>49,1; 49,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,81; 49,36</t>
+          <t>49,06; 49,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,04; 49,41</t>
+          <t>49,05; 49,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,82; 49,18</t>
+          <t>48,84; 49,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,18; 49,54</t>
+          <t>49,2; 49,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,22; 50,07</t>
+          <t>49,13; 49,41</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59,23</t>
+          <t>59,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59,14</t>
+          <t>59,15</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,19</t>
+          <t>59,18</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,55; 60,17</t>
+          <t>59,56; 60,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,95; 59,58</t>
+          <t>58,96; 59,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,01; 59,46</t>
+          <t>59,0; 59,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,22; 59,83</t>
+          <t>59,23; 59,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,07; 59,69</t>
+          <t>59,08; 59,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,29; 59,86</t>
+          <t>59,31; 59,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,97; 59,31</t>
+          <t>58,95; 59,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,47; 59,91</t>
+          <t>59,48; 59,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,09; 59,56</t>
+          <t>59,11; 59,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,2; 59,63</t>
+          <t>59,21; 59,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,05; 59,35</t>
+          <t>59,03; 59,32</t>
         </is>
       </c>
     </row>
@@ -1363,47 +1363,47 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>69,31</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,03</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,97</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,29</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>69,18</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69,11</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>69,32</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>69,3</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,03</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,97</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,29</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>68,45</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>69,11</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>69,32</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>69,3</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,77</t>
+          <t>69,24</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,86; 69,58</t>
+          <t>68,89; 69,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,35; 70,04</t>
+          <t>69,36; 70,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,05; 69,66</t>
+          <t>69,02; 69,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 69,56</t>
+          <t>69,07; 69,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,78; 69,35</t>
+          <t>68,7; 69,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,66; 69,29</t>
+          <t>68,67; 69,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69,0; 69,59</t>
+          <t>68,96; 69,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67,63; 69,24</t>
+          <t>68,99; 69,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,88; 69,33</t>
+          <t>68,89; 69,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 69,54</t>
+          <t>69,09; 69,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 69,52</t>
+          <t>69,08; 69,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67,93; 69,31</t>
+          <t>69,09; 69,4</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81,55</t>
+          <t>81,44</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,08</t>
+          <t>82,07</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,86</t>
+          <t>81,82</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,78; 79,93</t>
+          <t>78,82; 80,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,26; 80,37</t>
+          <t>79,26; 80,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,78; 80,68</t>
+          <t>79,76; 80,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81,09; 82,01</t>
+          <t>80,99; 81,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,32; 79,13</t>
+          <t>78,31; 79,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,42; 80,36</t>
+          <t>79,43; 80,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,76; 80,88</t>
+          <t>79,76; 80,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81,69; 82,53</t>
+          <t>81,63; 82,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,64; 79,3</t>
+          <t>78,65; 79,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79,46; 80,18</t>
+          <t>79,49; 80,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79,88; 80,64</t>
+          <t>79,9; 80,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,56; 82,19</t>
+          <t>81,53; 82,1</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48,59</t>
+          <t>48,51</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51,04</t>
+          <t>50,24</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49,86</t>
+          <t>49,4</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,79; 44,04</t>
+          <t>42,8; 44,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,16; 45,35</t>
+          <t>44,1; 45,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,43; 46,58</t>
+          <t>45,4; 46,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,7; 49,36</t>
+          <t>47,8; 49,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,11; 46,39</t>
+          <t>45,18; 46,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,43; 47,66</t>
+          <t>46,43; 47,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,66; 48,92</t>
+          <t>47,6; 48,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,79; 53,85</t>
+          <t>49,65; 50,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44,17; 45,06</t>
+          <t>44,13; 45,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45,48; 46,36</t>
+          <t>45,56; 46,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,73; 47,57</t>
+          <t>46,76; 47,64</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,09; 51,61</t>
+          <t>48,96; 49,88</t>
         </is>
       </c>
     </row>
